--- a/naver-place-crawler/results_health/안양_헬스장.xlsx
+++ b/naver-place-crawler/results_health/안양_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,57 +559,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피아트짐 헬스&amp;PT 평촌점</t>
+          <t>하이랙스 평촌점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>stuff7561@naver.com</t>
+          <t>hi-rax@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1383-7998</t>
+          <t>0507-1330-8530</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관평로182번길 48 신세대상가 지하1층</t>
+          <t>경기 안양시 동안구 시민대로 214 2층 203호 하이랙스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://hi-rax.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qkb1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="Q2" t="n">
-        <v>733</v>
+        <v>55</v>
       </c>
       <c r="R2" t="n">
-        <v>972</v>
+        <v>373</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,73 +640,81 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2047793712</t>
+          <t>1955456223</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047793712</t>
+          <t>https://m.place.naver.com/place/1955456223</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인싸짐 관양점 헬스 PT</t>
+          <t>라인짐 휘트니스 평촌점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mukiwihaeundoung@naver.com</t>
+          <t>btchojja@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1369-6019</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 346 2층</t>
+          <t>경기 안양시 동안구 부림로 171 라츠오피스텔 219호 라인짐휘트니스평촌점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inssagwanyang?igsh=MTR4d3VmNGt5eGw0ZA==</t>
+          <t>http://www.linegym.co.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dovh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>595</v>
+        <v>495</v>
       </c>
       <c r="Q3" t="n">
-        <v>2596</v>
+        <v>3176</v>
       </c>
       <c r="R3" t="n">
-        <v>3191</v>
+        <v>3671</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1360937972</t>
+          <t>1697812751</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1360937972</t>
+          <t>https://m.place.naver.com/place/1697812751</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더메이커짐 헬스&amp;PT 안양본점</t>
+          <t>스포애니 범계역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>themakergym1211@naver.com</t>
+          <t>spoany_24@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1414-1222</t>
+          <t>0507-1413-9618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 문예로 35 지하1층</t>
+          <t>경기 안양시 동안구 시민대로 167 안양벤처텔 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.maker.gym_anyang</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -790,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49pce</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>415</v>
+        <v>2187</v>
       </c>
       <c r="Q4" t="n">
-        <v>1086</v>
+        <v>2453</v>
       </c>
       <c r="R4" t="n">
-        <v>1501</v>
+        <v>4640</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,24 +836,24 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1195111809</t>
+          <t>36123678</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1195111809</t>
+          <t>https://m.place.naver.com/place/36123678</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -884,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cnd9</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -899,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="Q5" t="n">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="R5" t="n">
-        <v>2659</v>
+        <v>2672</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -924,41 +944,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스89 헬스&amp;PT 내손점</t>
+          <t>피아트짐 헬스&amp;PT 평촌점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitness89_gym@naver.com</t>
+          <t>alsrl6309-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1375-9004</t>
+          <t>0507-1383-7998</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 포일로 8 미성 빌딩 2층</t>
+          <t>경기 안양시 동안구 관평로182번길 48 신세대상가 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness89_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzpxnw9</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1336</v>
+        <v>246</v>
       </c>
       <c r="Q6" t="n">
-        <v>3331</v>
+        <v>758</v>
       </c>
       <c r="R6" t="n">
-        <v>4667</v>
+        <v>1004</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,56 +1032,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1471306408</t>
+          <t>2047793712</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471306408</t>
+          <t>https://m.place.naver.com/place/2047793712</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>골드에이피트니스 안양점 헬스 PT 필라테스</t>
+          <t>빅브로짐 범계점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goldaaa2020@naver.com</t>
+          <t>bigbrogym_beomgye@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1369-0183</t>
+          <t>0507-1410-3514</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 283 안양빌딩 7층</t>
+          <t>경기 안양시 동안구 시민대로 161 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goldaaa2020</t>
+          <t>https://bigbrogym.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1072,13 +1096,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wg6m5fg</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1160</v>
+        <v>2245</v>
       </c>
       <c r="Q7" t="n">
-        <v>1073</v>
+        <v>1917</v>
       </c>
       <c r="R7" t="n">
-        <v>2233</v>
+        <v>4162</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160243355</t>
+          <t>1533873958</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160243355</t>
+          <t>https://m.place.naver.com/place/1533873958</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비오엠 범계점 PT 헬스</t>
+          <t>김관장의착한PT 관양동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fitnessbom@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-5144</t>
+          <t>0507-1475-3481</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,20 +1184,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wit2oyw</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1259</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="n">
-        <v>1337</v>
+        <v>412</v>
       </c>
       <c r="R8" t="n">
-        <v>2596</v>
+        <v>491</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1206984359</t>
+          <t>2033189234</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206984359</t>
+          <t>https://m.place.naver.com/place/2033189234</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비앤핏 플레티넘 헬스&amp;PT 관양동점</t>
+          <t>김관장의착한PT 호계동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jeongk0126@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1407-8868</t>
+          <t>0507-1393-3519</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 488 203호</t>
+          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bienfit_come</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1260,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5trfo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>218</v>
+        <v>1793</v>
       </c>
       <c r="Q9" t="n">
-        <v>896</v>
+        <v>672</v>
       </c>
       <c r="R9" t="n">
-        <v>1114</v>
+        <v>2465</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,74 +1326,78 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37879656</t>
+          <t>1954358336</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37879656</t>
+          <t>https://m.place.naver.com/place/1954358336</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>빅브로짐 헬스&amp;PT 평촌점</t>
+          <t>유온짐 피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bigbrogym_pyeongchon@naver.com</t>
+          <t>uongym_1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1367-9689</t>
+          <t>0507-1315-9023</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관평로182번길 30 B1</t>
+          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://bigbrogym.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wtmpo6z</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1795</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2550</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>4345</v>
+        <v>4</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1282202314</t>
+          <t>2017252486</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282202314</t>
+          <t>https://m.place.naver.com/place/2017252486</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1406,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
+          <t>레몬짐 안양점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>baeggops@naver.com</t>
+          <t>lafcompany_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1424-1777</t>
+          <t>031-441-7779</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 45 8층</t>
+          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baeggops</t>
+          <t>http://www.lemongym.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1448,13 +1488,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzswuhw</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1340</v>
+        <v>633</v>
       </c>
       <c r="Q11" t="n">
-        <v>936</v>
+        <v>898</v>
       </c>
       <c r="R11" t="n">
-        <v>2276</v>
+        <v>1531</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1351894889</t>
+          <t>1417153496</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351894889</t>
+          <t>https://m.place.naver.com/place/1417153496</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라이프피트니스 안양 헬스 PT 필라테스 요가</t>
+          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lifeanyang@naver.com</t>
+          <t>baeggops@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1440-7782</t>
+          <t>0507-1424-1777</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 311 5, 6층</t>
+          <t>경기 안양시 동안구 평촌대로217번길 45 8층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lifeanyang</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,20 +1576,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45a99</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1192</v>
+        <v>1342</v>
       </c>
       <c r="Q12" t="n">
-        <v>492</v>
+        <v>954</v>
       </c>
       <c r="R12" t="n">
-        <v>1684</v>
+        <v>2296</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,863 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1929733993</t>
+          <t>1351894889</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1929733993</t>
+          <t>https://m.place.naver.com/place/1351894889</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>라인짐 휘트니스 평촌점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>btchojja@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1369-6019</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 부림로 171 라츠오피스텔 219호 라인짐휘트니스평촌점</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>http://www.linegym.co.kr</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>498</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3137</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3635</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1697812751</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1697812751</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>피트니스89 안양점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>fitness89_gym4@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1353-3999</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 안양시 만안구 안양로329번길 108 5층 501~504호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitness89_gym4</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>693</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2693</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3386</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1875611572</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1875611572</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>스포애니 범계역점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>spoany_24@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1413-9618</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 시민대로 167 안양벤처텔 10층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/spoany_24</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>2171</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2419</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4590</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>36123678</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/36123678</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>빅브로짐 범계점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bigbrogym_beomgye@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1410-3514</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 시민대로 161 10층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://bigbrogym.com</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>2236</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1910</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4146</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1533873958</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1533873958</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>여성전용피트니스 디메이드 평촌점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>demadefit2@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1362-2146</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 관평로182번길 23 무지개프라자 5층 505호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/de_made_fit_pch</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>160</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>300</v>
-      </c>
-      <c r="R17" t="n">
-        <v>460</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2039306968</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2039306968</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>엑셀휘트니스 PT 평촌점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>xcellfitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1371-2614</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 시민대로327번길 7 대명글로벌 비즈스퀘어 B1 102호</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/xcellfitness2</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1424</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1421</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2845</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1648067374</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1648067374</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MVM피트니스 PT&amp;필라테스 안양평촌점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>fitness_anyang@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1355-8821</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 경수대로 597 영신빌딩 3층, 4층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitness_anyang</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1969</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1371</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3340</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1925453539</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1925453539</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>블랙짐 관양점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>blackgym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1494-2262</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 관평로 312 4층 블랙짐</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/blackgym2</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>552</v>
-      </c>
-      <c r="R20" t="n">
-        <v>869</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>994818861</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/994818861</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>자마이카피트니스앤스파 범계역점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>jamaica3651@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1430-8533</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 평촌대로243번길 30 샤크존빌딩 2층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>http://www.jfk01.co.kr</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1556</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>227</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1783</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1235220033</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1235220033</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_헬스장.xlsx
+++ b/naver-place-crawler/results_health/안양_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q2" t="n">
         <v>55</v>
       </c>
       <c r="R2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>495</v>
       </c>
       <c r="Q3" t="n">
-        <v>3176</v>
+        <v>3190</v>
       </c>
       <c r="R3" t="n">
-        <v>3671</v>
+        <v>3685</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2187</v>
+        <v>2193</v>
       </c>
       <c r="Q4" t="n">
-        <v>2453</v>
+        <v>2458</v>
       </c>
       <c r="R4" t="n">
-        <v>4640</v>
+        <v>4651</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -880,17 +880,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnFnxeK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="Q5" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="R5" t="n">
-        <v>2672</v>
+        <v>2679</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,44 +956,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피아트짐 헬스&amp;PT 평촌점</t>
+          <t>빅브로짐 범계점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alsrl6309-@naver.com</t>
+          <t>bigbrogym_beomgye@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1383-7998</t>
+          <t>0507-1410-3514</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 관평로182번길 48 신세대상가 지하1층</t>
+          <t>경기 안양시 동안구 시민대로 161 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://bigbrogym.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzpxnw9</t>
+          <t>https://talk.naver.com/ct/wg6m5fg</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>246</v>
+        <v>2247</v>
       </c>
       <c r="Q6" t="n">
-        <v>758</v>
+        <v>1933</v>
       </c>
       <c r="R6" t="n">
-        <v>1004</v>
+        <v>4180</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,66 +1032,66 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2047793712</t>
+          <t>1533873958</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047793712</t>
+          <t>https://m.place.naver.com/place/1533873958</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빅브로짐 범계점</t>
+          <t>비오엠 범계점 PT 헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bigbrogym_beomgye@naver.com</t>
+          <t>fitnessbom@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1410-3514</t>
+          <t>0507-1374-5144</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 161 10층</t>
+          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://bigbrogym.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg6m5fg</t>
+          <t>https://talk.naver.com/ct/w4cd0d</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2245</v>
+        <v>1265</v>
       </c>
       <c r="Q7" t="n">
-        <v>1917</v>
+        <v>1357</v>
       </c>
       <c r="R7" t="n">
-        <v>4162</v>
+        <v>2622</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1533873958</t>
+          <t>1206984359</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533873958</t>
+          <t>https://m.place.naver.com/place/1206984359</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,24 +1152,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>김관장의착한PT 관양동점</t>
+          <t>유온짐 피트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>uongym_1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1475-3481</t>
+          <t>0507-1315-9023</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
+          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wit2oyw</t>
+          <t>https://talk.naver.com/ct/wtmpo6z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>412</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>491</v>
+        <v>8</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2033189234</t>
+          <t>2017252486</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033189234</t>
+          <t>https://m.place.naver.com/place/2017252486</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,24 +1250,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>김관장의착한PT 호계동점</t>
+          <t>헬스&amp;PT 하이얼짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>higher_gym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1393-3519</t>
+          <t>0507-1303-2298</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
+          <t>경기 안양시 만안구 전파로 24 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5trfo</t>
+          <t>https://talk.naver.com/ct/whocbqe</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1793</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>672</v>
+        <v>23</v>
       </c>
       <c r="R9" t="n">
-        <v>2465</v>
+        <v>49</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,61 +1326,61 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1954358336</t>
+          <t>2037213524</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954358336</t>
+          <t>https://m.place.naver.com/place/2037213524</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유온짐 피트니스</t>
+          <t>테이스트피트니스 헬스&amp;PT 24시 안양예술공원점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uongym_1@naver.com</t>
+          <t>tasteay@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1315-9023</t>
+          <t>0507-1330-9025</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
+          <t>경기 안양시 만안구 경수대로 1176 4층 테이스트 피트니스 안양예술공원점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xkhxhDn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,27 +1395,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtmpo6z</t>
+          <t>https://talk.naver.com/ct/wut4nw3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2017252486</t>
+          <t>2028902532</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017252486</t>
+          <t>https://m.place.naver.com/place/2028902532</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가,명상</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레몬짐 안양점 PT&amp;헬스</t>
+          <t>요가하라 범계역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lafcompany_@naver.com</t>
+          <t>yogahara2019@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-441-7779</t>
+          <t>0507-1392-7282</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
+          <t>경기 안양시 동안구 시민대로 199 6층 601호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.lemongym.co.kr</t>
+          <t>https://yogahara.page24.app/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzswuhw</t>
+          <t>https://talk.naver.com/ct/w5y07f</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>633</v>
+        <v>193</v>
       </c>
       <c r="Q11" t="n">
-        <v>898</v>
+        <v>169</v>
       </c>
       <c r="R11" t="n">
-        <v>1531</v>
+        <v>362</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,115 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1417153496</t>
+          <t>1457104015</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417153496</t>
+          <t>https://m.place.naver.com/place/1457104015</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>baeggops@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1424-1777</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 안양시 동안구 평촌대로217번길 45 8층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45a99</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1342</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>954</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2296</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1351894889</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1351894889</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_헬스장.xlsx
+++ b/naver-place-crawler/results_health/안양_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>하이랙스 평촌점</t>
+          <t>헬스코인 인덕원점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hi-rax@naver.com</t>
+          <t>health_coin@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-8530</t>
+          <t>0507-1381-1413</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 214 2층 203호 하이랙스</t>
+          <t>경기 안양시 동안구 흥안대로414번길 21-25 2층 헬스코인</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://hi-rax.com/</t>
+          <t>https://blog.naver.com/health_coin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qkb1</t>
+          <t>https://talk.naver.com/ct/w4feal</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>319</v>
+        <v>466</v>
       </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="R2" t="n">
-        <v>374</v>
+        <v>563</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1955456223</t>
+          <t>1286730922</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955456223</t>
+          <t>https://m.place.naver.com/place/1286730922</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>495</v>
       </c>
       <c r="Q3" t="n">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="R3" t="n">
-        <v>3685</v>
+        <v>3686</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xnFnxeK</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1020,10 +1020,10 @@
         <v>2247</v>
       </c>
       <c r="Q6" t="n">
-        <v>1933</v>
+        <v>1938</v>
       </c>
       <c r="R6" t="n">
-        <v>4180</v>
+        <v>4185</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessbom</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1152,44 +1152,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유온짐 피트니스</t>
+          <t>하이랙스 평촌점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>uongym_1@naver.com</t>
+          <t>hi-rax@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1315-9023</t>
+          <t>0507-1330-8530</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
+          <t>경기 안양시 동안구 시민대로 214 2층 203호 하이랙스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://hi-rax.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtmpo6z</t>
+          <t>https://talk.naver.com/ct/w4qkb1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>319</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2017252486</t>
+          <t>1955456223</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017252486</t>
+          <t>https://m.place.naver.com/place/1955456223</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 하이얼짐</t>
+          <t>김관장의착한PT 관양동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>higher_gym1@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1303-2298</t>
+          <t>0507-1475-3481</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 전파로 24 3층</t>
+          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/5director.kim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whocbqe</t>
+          <t>https://talk.naver.com/ct/wit2oyw</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>412</v>
       </c>
       <c r="R9" t="n">
-        <v>49</v>
+        <v>491</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2037213524</t>
+          <t>2033189234</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037213524</t>
+          <t>https://m.place.naver.com/place/2033189234</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>테이스트피트니스 헬스&amp;PT 24시 안양예술공원점</t>
+          <t>김관장의착한PT 호계동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tasteay@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1330-9025</t>
+          <t>0507-1393-3519</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 경수대로 1176 4층 테이스트 피트니스 안양예술공원점</t>
+          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xkhxhDn</t>
+          <t>https://blog.naver.com/thekindpt2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wut4nw3</t>
+          <t>https://talk.naver.com/ct/w5trfo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>268</v>
+        <v>1802</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>672</v>
       </c>
       <c r="R10" t="n">
-        <v>295</v>
+        <v>2474</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2028902532</t>
+          <t>1954358336</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028902532</t>
+          <t>https://m.place.naver.com/place/1954358336</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,96 +1441,194 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>요가,명상</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>요가하라 범계역점</t>
+          <t>유온짐 피트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yogahara2019@naver.com</t>
+          <t>uongym_1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1392-7282</t>
+          <t>0507-1315-9023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uongym_1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wtmpo6z</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2017252486</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2017252486</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>요가,명상</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>요가하라 범계역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yogahara2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1392-7282</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>경기 안양시 동안구 시민대로 199 6층 601호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://yogahara.page24.app/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5y07f</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>193</v>
       </c>
-      <c r="Q11" t="n">
-        <v>169</v>
-      </c>
-      <c r="R11" t="n">
-        <v>362</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>168</v>
+      </c>
+      <c r="R12" t="n">
+        <v>361</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1457104015</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1457104015</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/안양_헬스장.xlsx
+++ b/naver-place-crawler/results_health/안양_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스포애니 범계역점</t>
+          <t>인싸짐 관양점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>spoany_24@naver.com</t>
+          <t>choojy6017@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1413-9618</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 167 안양벤처텔 10층</t>
+          <t>경기 안양시 동안구 관악대로 346 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +592,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49pce</t>
+          <t>https://talk.naver.com/ct/wvqiqz2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2200</v>
+        <v>605</v>
       </c>
       <c r="Q2" t="n">
-        <v>2465</v>
+        <v>2662</v>
       </c>
       <c r="R2" t="n">
-        <v>4665</v>
+        <v>3267</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>36123678</t>
+          <t>1360937972</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36123678</t>
+          <t>https://m.place.naver.com/place/1360937972</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,39 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>라인짐 휘트니스 평촌점</t>
+          <t>인싸짐 석수점 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>btchojja@naver.com</t>
+          <t>healthyboboo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1369-6019</t>
+          <t>0507-1389-3818</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 부림로 171 라츠오피스텔 219호 라인짐휘트니스평촌점</t>
+          <t>경기 안양시 만안구 안양로 511 5, 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.linegym.co.kr</t>
+          <t>https://blog.naver.com/healthyboboo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,12 +705,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dovh</t>
+          <t>https://talk.naver.com/ct/w5z1oi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>495</v>
+        <v>1408</v>
       </c>
       <c r="Q3" t="n">
-        <v>3194</v>
+        <v>1013</v>
       </c>
       <c r="R3" t="n">
-        <v>3689</v>
+        <v>2421</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,61 +734,61 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1697812751</t>
+          <t>1489968796</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697812751</t>
+          <t>https://m.place.naver.com/place/1489968796</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비오엠 안양점 PT 헬스 필라테스</t>
+          <t>스포애니 범계역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitnessbom2@naver.com</t>
+          <t>spoany_24@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1371-5144</t>
+          <t>0507-1413-9618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>경기 안양시 동안구 시민대로 167 안양벤처텔 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnFnxeK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cnd9</t>
+          <t>https://talk.naver.com/ct/w49pce</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1519</v>
+        <v>2201</v>
       </c>
       <c r="Q4" t="n">
-        <v>1161</v>
+        <v>2466</v>
       </c>
       <c r="R4" t="n">
-        <v>2680</v>
+        <v>4667</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1685119758</t>
+          <t>36123678</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685119758</t>
+          <t>https://m.place.naver.com/place/36123678</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>빅브로짐 범계점</t>
+          <t>라인짐 휘트니스 평촌점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bigbrogym_beomgye@naver.com</t>
+          <t>btchojja@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1410-3514</t>
+          <t>0507-1369-6019</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 161 10층</t>
+          <t>경기 안양시 동안구 부림로 171 라츠오피스텔 219호 라인짐휘트니스평촌점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://bigbrogym.com</t>
+          <t>http://www.linegym.co.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wg6m5fg</t>
+          <t>https://talk.naver.com/ct/w4dovh</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2246</v>
+        <v>495</v>
       </c>
       <c r="Q5" t="n">
-        <v>1955</v>
+        <v>3195</v>
       </c>
       <c r="R5" t="n">
-        <v>4201</v>
+        <v>3690</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +930,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1533873958</t>
+          <t>1697812751</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533873958</t>
+          <t>https://m.place.naver.com/place/1697812751</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스89 안양점</t>
+          <t>비오엠 안양점 PT 헬스 필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitness89_gym4@naver.com</t>
+          <t>fitnessbom2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1353-3999</t>
+          <t>0507-1371-5144</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 안양로329번길 108 5층 501~504호</t>
+          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness89_gym4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,23 +984,27 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cnd9</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>711</v>
+        <v>1519</v>
       </c>
       <c r="Q6" t="n">
-        <v>3010</v>
+        <v>1161</v>
       </c>
       <c r="R6" t="n">
-        <v>3721</v>
+        <v>2680</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1875611572</t>
+          <t>1685119758</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875611572</t>
+          <t>https://m.place.naver.com/place/1685119758</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유온짐 피트니스</t>
+          <t>빅브로짐 범계점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uongym_1@naver.com</t>
+          <t>bigbrogym_beomgye@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1315-9023</t>
+          <t>0507-1410-3514</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 만안로 241 7,8,9층</t>
+          <t>경기 안양시 동안구 시민대로 161 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uongym_1</t>
+          <t>https://bigbrogym.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtmpo6z</t>
+          <t>https://talk.naver.com/ct/wg6m5fg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>2246</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>1957</v>
       </c>
       <c r="R7" t="n">
-        <v>11</v>
+        <v>4203</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,81 +1126,77 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2017252486</t>
+          <t>1533873958</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017252486</t>
+          <t>https://m.place.naver.com/place/1533873958</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레몬짐 안양점 PT&amp;헬스</t>
+          <t>피트니스89 안양점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lafcompany_@naver.com</t>
+          <t>fitness89_gym4@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-441-7779</t>
+          <t>0507-1353-3999</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
+          <t>경기 안양시 만안구 안양로329번길 108 5층 501~504호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.lemongym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzswuhw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>634</v>
+        <v>711</v>
       </c>
       <c r="Q8" t="n">
-        <v>898</v>
+        <v>3016</v>
       </c>
       <c r="R8" t="n">
-        <v>1532</v>
+        <v>3727</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,56 +1220,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1417153496</t>
+          <t>1875611572</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417153496</t>
+          <t>https://m.place.naver.com/place/1875611572</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
+          <t>레몬짐 안양점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>baeggops@naver.com</t>
+          <t>lafcompany_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1424-1777</t>
+          <t>031-441-7779</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 평촌대로217번길 45 8층</t>
+          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baeggops</t>
+          <t>http://www.lemongym.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1293,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45a99</t>
+          <t>https://talk.naver.com/ct/wzswuhw</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1341</v>
+        <v>635</v>
       </c>
       <c r="Q9" t="n">
-        <v>959</v>
+        <v>898</v>
       </c>
       <c r="R9" t="n">
-        <v>2300</v>
+        <v>1533</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1351894889</t>
+          <t>1417153496</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351894889</t>
+          <t>https://m.place.naver.com/place/1417153496</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1344,30 +1340,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>인싸짐 관양점 헬스 PT</t>
+          <t>머스타드 피트니스 안양비산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mukiwihaeundoung@naver.com</t>
+          <t>mustard_bisan@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1477-8964</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 관악대로 346 2층</t>
+          <t>경기 안양시 동안구 관악대로 133</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inssagwanyang?igsh=MTR4d3VmNGt5eGw0ZA==</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wvqiqz2</t>
+          <t>https://talk.naver.com/ct/w5itxg</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>605</v>
+        <v>2259</v>
       </c>
       <c r="Q10" t="n">
-        <v>2661</v>
+        <v>220</v>
       </c>
       <c r="R10" t="n">
-        <v>3266</v>
+        <v>2479</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,115 +1416,213 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1360937972</t>
+          <t>1005836630</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1360937972</t>
+          <t>https://m.place.naver.com/place/1005836630</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>요가,명상</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>요가하라 범계역점</t>
+          <t>비오엠 범계점 PT 헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yogahara2019@naver.com</t>
+          <t>fitnessbom@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1392-7282</t>
+          <t>0507-1374-5144</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cd0d</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1266</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1360</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2626</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1206984359</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206984359</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>요가,명상</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>요가하라 범계역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yogahara2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1392-7282</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>경기 안양시 동안구 시민대로 199 6층 601호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://yogahara.page24.app/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5y07f</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>193</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>168</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>361</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1457104015</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1457104015</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
